--- a/aluminium_data.xlsx
+++ b/aluminium_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\703445113\Desktop\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8254EC0-5904-4FE4-9309-7524F006C99F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC7814D7-AF10-4645-BD0A-1644F5F6D05A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Parts" sheetId="1" r:id="rId1"/>
@@ -592,7 +592,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -607,12 +607,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -659,7 +653,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -701,16 +695,13 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3087,8 +3078,8 @@
       <c r="B31" s="2"/>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A33" s="19"/>
-      <c r="B33" s="20"/>
+      <c r="A33" s="18"/>
+      <c r="B33" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3183,7 +3174,7 @@
       <c r="A9" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="B9" s="22">
+      <c r="B9" s="4">
         <v>1.1142000000000001</v>
       </c>
     </row>
@@ -3191,7 +3182,7 @@
       <c r="A10" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="B10" s="22">
+      <c r="B10" s="4">
         <v>1.1618999999999999</v>
       </c>
     </row>
@@ -3226,7 +3217,7 @@
       <c r="B14" s="4">
         <v>1.08</v>
       </c>
-      <c r="C14" s="21"/>
+      <c r="C14" s="17"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
@@ -3235,7 +3226,7 @@
       <c r="B15" s="4">
         <v>1</v>
       </c>
-      <c r="C15" s="21"/>
+      <c r="C15" s="17"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
@@ -3244,7 +3235,7 @@
       <c r="B16" s="4">
         <v>1.0886</v>
       </c>
-      <c r="C16" s="21"/>
+      <c r="C16" s="17"/>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
@@ -3253,7 +3244,7 @@
       <c r="B17" s="4">
         <v>1.0772999999999999</v>
       </c>
-      <c r="C17" s="21"/>
+      <c r="C17" s="17"/>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" s="3" t="s">
@@ -3262,7 +3253,7 @@
       <c r="B18" s="4">
         <v>1.0772999999999999</v>
       </c>
-      <c r="C18" s="21"/>
+      <c r="C18" s="17"/>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
@@ -3271,7 +3262,7 @@
       <c r="B19" s="4">
         <v>1.0772999999999999</v>
       </c>
-      <c r="C19" s="21"/>
+      <c r="C19" s="17"/>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" s="3" t="s">
@@ -3280,7 +3271,7 @@
       <c r="B20" s="4">
         <v>1.0705</v>
       </c>
-      <c r="C20" s="21"/>
+      <c r="C20" s="17"/>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" s="3" t="s">
@@ -3289,7 +3280,7 @@
       <c r="B21" s="4">
         <v>1.0705</v>
       </c>
-      <c r="C21" s="21"/>
+      <c r="C21" s="17"/>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" s="3" t="s">
@@ -3298,7 +3289,7 @@
       <c r="B22" s="4">
         <v>1.0705</v>
       </c>
-      <c r="C22" s="21"/>
+      <c r="C22" s="17"/>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" s="3" t="s">
@@ -3307,7 +3298,7 @@
       <c r="B23" s="4">
         <v>1.0705</v>
       </c>
-      <c r="C23" s="21"/>
+      <c r="C23" s="17"/>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" s="3" t="s">
@@ -3316,7 +3307,7 @@
       <c r="B24" s="4">
         <v>1.0705</v>
       </c>
-      <c r="C24" s="21"/>
+      <c r="C24" s="17"/>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" s="3" t="s">
@@ -3325,7 +3316,7 @@
       <c r="B25" s="4">
         <v>1.0705</v>
       </c>
-      <c r="C25" s="21"/>
+      <c r="C25" s="17"/>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" s="3" t="s">
@@ -3334,7 +3325,7 @@
       <c r="B26" s="4">
         <v>1.0659000000000001</v>
       </c>
-      <c r="C26" s="21"/>
+      <c r="C26" s="17"/>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" s="3" t="s">
@@ -3343,7 +3334,7 @@
       <c r="B27" s="4">
         <v>1.0659000000000001</v>
       </c>
-      <c r="C27" s="21"/>
+      <c r="C27" s="17"/>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" s="3" t="s">
@@ -3352,7 +3343,7 @@
       <c r="B28" s="4">
         <v>1.0659000000000001</v>
       </c>
-      <c r="C28" s="21"/>
+      <c r="C28" s="17"/>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" s="6"/>
@@ -3367,8 +3358,8 @@
       <c r="B31" s="7"/>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A33" s="19"/>
-      <c r="B33" s="20"/>
+      <c r="A33" s="18"/>
+      <c r="B33" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3648,8 +3639,8 @@
       <c r="B32" s="6"/>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A33" s="17"/>
-      <c r="B33" s="18"/>
+      <c r="A33" s="20"/>
+      <c r="B33" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3914,8 +3905,8 @@
       <c r="B32" s="6"/>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A33" s="17"/>
-      <c r="B33" s="18"/>
+      <c r="A33" s="20"/>
+      <c r="B33" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="1">
